--- a/stories/arbres/TREE-DIF-009.xlsx
+++ b/stories/arbres/TREE-DIF-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est dans le train, avec papa. Maman les attend à la gare. Un enfant plus grand tient un ticket. Un enfant plus petit tient un doudou. Les tailles sont différentes. Papa dit : on invite. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Kenzo est dans le train, avec papa. Maman les attend à la gare. Un enfant plus grand tient un ticket. Un enfant plus petit tient un doudou. Les tailles sont différentes. On invite. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est dans le train, avec papa. Maman les attend à la gare. Un enfant plus grand tient un ticket. Un enfant plus petit tient un doudou. Les tailles sont différentes.
+papa|On invite. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Kenzo va vers la cuisine du wagon. Un copain plus grand tient une brioche. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Papa sourit. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On joue ensemble ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Kenzo respire. Papa est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose le ballon rouge sur la tablette. Un copain plus grand le fait rouler, tout doux. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la cuisine. Puis le ballon rouge. Puis Tom. On rit un peu. Kenzo chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Une tasse cliquette. Kenzo essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un ruban reste dans la poche. Kenzo montre Sami à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3615,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose le seau bleu entre les sièges. Un copain plus petit tient l'anse. On joue ensemble. Papa dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Kenzo pose le seau bleu entre les sièges. Un copain plus petit tient l'anse. On joue ensemble. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3753,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose le seau bleu entre les sièges. Un copain plus petit tient l'anse. On joue ensemble.
+papa|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3948,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4117,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Kenzo s'arrête. On range un objet. Kenzo ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range le seau bleu. Léa reste près de la cuisine. Un ballon s'immobilise. Maman n'est pas loin. Kenzo les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Il y a des miettes sur la table. Kenzo plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5119,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose le doudou sur les genoux. Un copain d'une autre taille le caresse. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5312,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5481,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la cuisine est fini. On se tient la main. Kenzo pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5648,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5815,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Kenzo pose le doudou. la cuisine est derrière. Le vent est doux. Kenzo range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5982,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6149,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre Sami. Papa a vu la cuisine. Et le doudou. Un chat miaule une fois. Kenzo raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6316,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6345,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Dans le train, Kenzo imagine le jardin derrière la vitre. Un copain plus petit montre un arbre. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Papa dit : je suis là. On peut jouer ensemble.</t>
+          <t>Dans le train, Kenzo imagine le jardin derrière la vitre. Un copain plus petit montre un arbre. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Je suis là. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6483,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Kenzo imagine le jardin derrière la vitre. Un copain plus petit montre un arbre. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes.
+papa|Je suis là. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6669,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6842,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Kenzo retient le geste. Papa sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7033,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7062,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kenzo fait rouler le ballon rouge près de la vitre. Un copain plus grand le rattrape. Les tailles sont différentes. Papa dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Kenzo fait rouler le ballon rouge près de la vitre. Un copain plus grand le rattrape. Les tailles sont différentes. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7200,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo fait rouler le ballon rouge près de la vitre. Un copain plus grand le rattrape. Les tailles sont différentes.
+papa|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le jardin. Puis le ballon rouge. Puis Tom. On dit merci. Kenzo souffle, puis sourit à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Le sol est un peu froid. Kenzo serre la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de le jardin. Et de le ballon rouge. Et de Sami. Une cloche tinte, tout loin. Kenzo range le jardin dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose le seau bleu. Un copain plus petit rit un peu. Les tailles sont différentes. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Kenzo s'arrête. Un galet est encore chaud. Kenzo s'assoit près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range le seau bleu. Léa reste près de le jardin. Une feuille tombe. Kenzo range encore un peu, près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Ça sent le pain chaud. Kenzo ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo assoit le doudou. Un copain d'une autre taille chuchote. Les tailles sont différentes. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. le jardin est fini. On écoute jusqu'au bout. Kenzo dit merci à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Kenzo pose le doudou. le jardin est derrière. Le savon sent bon. Kenzo boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre Sami. Papa a vu le jardin. Et le doudou. Un linge sèche à l'air. Kenzo caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10981,6 +11294,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Kenzo ouvre un livre de chambre. Un copain d'une autre taille s'assoit. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11475,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On invite, et on joue ensemble ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11648,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Kenzo hoche la tête. On continue, avec papa. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11839,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12006,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo fait un train : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11861,6 +12199,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12368,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la chambre. Puis le ballon rouge. Puis Tom. Une chaussette est encore sablée. Kenzo tend Tom à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12535,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12211,7 +12564,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de Léa. le ballon rouge est rangé. Un vélo passe au loin. Kenzo dit : j'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Kenzo s'arrête près de Léa. le ballon rouge est rangé. Un vélo passe au loin. J'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12349,6 +12702,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Un vélo passe au loin.
+enfant-m|J'ai appris.
+narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12871,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13038,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se souvient de la chambre. Et de le ballon rouge. Et de Sami. On entend un oiseau. Kenzo écoute papa encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13205,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12997,6 +13372,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo cache le seau bleu sous le siège. Un copain plus petit le retrouve. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13185,6 +13565,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13349,6 +13734,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Kenzo s'arrête. Les chaussures font toc toc. Kenzo répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13901,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14068,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo range le seau bleu. Léa reste près de la chambre. Une pomme brille un peu. Kenzo marche près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14235,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13997,6 +14402,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. La couverture est douce. Kenzo enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14569,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14183,7 +14598,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Kenzo calce le doudou. Un copain d'une autre taille sourit. Les tailles sont différentes. On joue ensemble. Papa dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Kenzo calce le doudou. Un copain d'une autre taille sourit. Les tailles sont différentes. On joue ensemble. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14321,6 +14736,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo calce le doudou. Un copain d'une autre taille sourit. Les tailles sont différentes. On joue ensemble.
+papa|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14509,6 +14931,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14673,6 +15100,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la chambre est fini. Un crochet tient bien le manteau. Kenzo sourit. Papa sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15267,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14997,6 +15434,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Kenzo pose le doudou. la chambre est derrière. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15601,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15768,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo montre Sami. Papa a vu la chambre. Et le doudou. La lumière est claire. Kenzo prend la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15935,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15574,6 +16031,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-009.xlsx
+++ b/stories/arbres/TREE-DIF-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On invite. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Dans le train, Kenzo va vers la cuisine du wagon. Un copain plus grand tient une brioche. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Papa sourit. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|On joue ensemble ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. On joue ensemble. Kenzo respire. Papa est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Kenzo pose le ballon rouge sur la tablette. Un copain plus grand le fait rouler, tout doux. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Kenzo a choisi la cuisine. Puis le ballon rouge. Puis Tom. On rit un peu. Kenzo chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Une tasse cliquette. Kenzo essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Kenzo se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un ruban reste dans la poche. Kenzo montre Sami à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3955,6 +3975,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4143,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Kenzo s'arrête. On range un objet. Kenzo ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4479,7 @@
           <t>narrateur|Kenzo range le seau bleu. Léa reste près de la cuisine. Un ballon s'immobilise. Maman n'est pas loin. Kenzo les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4815,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Il y a des miettes sur la table. Kenzo plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5151,7 @@
           <t>narrateur|Kenzo pose le doudou sur les genoux. Un copain d'une autre taille le caresse. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5347,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5486,6 +5515,7 @@
           <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la cuisine est fini. On se tient la main. Kenzo pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5653,6 +5683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5820,6 +5851,7 @@
           <t>narrateur|Près de Léa. Kenzo pose le doudou. la cuisine est derrière. Le vent est doux. Kenzo range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5987,6 +6019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6154,6 +6187,7 @@
           <t>narrateur|Kenzo montre Sami. Papa a vu la cuisine. Et le doudou. Un chat miaule une fois. Kenzo raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6321,6 +6355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6489,6 +6524,7 @@
 papa|Je suis là. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6676,6 +6712,7 @@
           <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6847,6 +6884,7 @@
           <t>narrateur|Oui. On joue ensemble. Kenzo retient le geste. Papa sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7038,6 +7076,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Kenzo a choisi le jardin. Puis le ballon rouge. Puis Tom. On dit merci. Kenzo souffle, puis sourit à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Le sol est un peu froid. Kenzo serre la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Kenzo se souvient de le jardin. Et de le ballon rouge. Et de Sami. Une cloche tinte, tout loin. Kenzo range le jardin dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Kenzo pose le seau bleu. Un copain plus petit rit un peu. Les tailles sont différentes. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Kenzo s'arrête. Un galet est encore chaud. Kenzo s'assoit près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Kenzo range le seau bleu. Léa reste près de le jardin. Une feuille tombe. Kenzo range encore un peu, près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Ça sent le pain chaud. Kenzo ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Kenzo assoit le doudou. Un copain d'une autre taille chuchote. Les tailles sont différentes. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. le jardin est fini. On écoute jusqu'au bout. Kenzo dit merci à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Près de Léa. Kenzo pose le doudou. le jardin est derrière. Le savon sent bon. Kenzo boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Kenzo montre Sami. Papa a vu le jardin. Et le doudou. Un linge sèche à l'air. Kenzo caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11299,6 +11362,7 @@
           <t>narrateur|Dans le train, Kenzo ouvre un livre de chambre. Un copain d'une autre taille s'assoit. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11482,6 +11546,7 @@
           <t>narrateur|On invite, et on joue ensemble ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11653,6 +11718,7 @@
           <t>narrateur|Oui. On joue ensemble. Kenzo hoche la tête. On continue, avec papa. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11844,6 +11910,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12011,6 +12078,7 @@
           <t>narrateur|Kenzo fait un train : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12206,6 +12274,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12373,6 +12442,7 @@
           <t>narrateur|Kenzo a choisi la chambre. Puis le ballon rouge. Puis Tom. Une chaussette est encore sablée. Kenzo tend Tom à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12540,6 +12610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12709,6 +12780,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12876,6 +12948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13043,6 +13116,7 @@
           <t>narrateur|Kenzo se souvient de la chambre. Et de le ballon rouge. Et de Sami. On entend un oiseau. Kenzo écoute papa encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13210,6 +13284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13377,6 +13452,7 @@
           <t>narrateur|Kenzo cache le seau bleu sous le siège. Un copain plus petit le retrouve. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13572,6 +13648,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13739,6 +13816,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Kenzo s'arrête. Les chaussures font toc toc. Kenzo répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13906,6 +13984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14073,6 +14152,7 @@
           <t>narrateur|Kenzo range le seau bleu. Léa reste près de la chambre. Une pomme brille un peu. Kenzo marche près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14240,6 +14320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14407,6 +14488,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. La couverture est douce. Kenzo enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14574,6 +14656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14743,6 +14826,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14938,6 +15022,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15105,6 +15190,7 @@
           <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la chambre est fini. Un crochet tient bien le manteau. Kenzo sourit. Papa sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15272,6 +15358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15439,6 +15526,7 @@
           <t>narrateur|Près de Léa. Kenzo pose le doudou. la chambre est derrière. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15606,6 +15694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15773,6 +15862,7 @@
           <t>narrateur|Kenzo montre Sami. Papa a vu la chambre. Et le doudou. La lumière est claire. Kenzo prend la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15940,6 +16030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15958,7 +16049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16038,6 +16129,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16239,6 +16344,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-009.xlsx
+++ b/stories/arbres/TREE-DIF-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plus petit ou plus grand — dans le train avec papa</t>
+          <t>Les rails chantent, Amir et Nina jouent</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les rails chantent. Amir voyage avec papa et maman. Nina est plus grande. Ils jouent ensemble dans le wagon, malgré des tailles différentes.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est dans le train, avec papa. Maman les attend à la gare. Un enfant plus grand tient un ticket. Un enfant plus petit tient un doudou. Les tailles sont différentes. On invite. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Les rails chantent sous le wagon. Un tunnel avale la lumière. Puis elle revient, toute claire. Le filet à bagages tremble, tout bas. Un manteau bleu pend, près de la porte. Ça sent l'orange, tout doux. Une peau repose sur la tablette. Le siège pique un peu les genoux. Un ticket dépasse de la poche de papa. Dehors, des vaches passent, toutes lentes. Maman plie un foulard bleu, sur ses genoux. Nina a un sac, tout près. Nina est plus grande. Amir est plus petit. Les tailles sont différentes. Tu as vu les vaches, Amir ? Oui, papa. Le foulard est pour la gare. En ce moment, Amir pose un doigt sur la tablette. La tablette vibre, tout doux. Viens jouer. Oui. On joue ensemble, d'accord ? D'accord. Les tailles sont différentes. Et on joue ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,8 +1337,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo est dans le train, avec papa. Maman les attend à la gare. Un enfant plus grand tient un ticket. Un enfant plus petit tient un doudou. Les tailles sont différentes.
-papa|On invite. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Les rails chantent sous le wagon.
+narrateur|Un tunnel avale la lumière.
+narrateur|Puis elle revient, toute claire.
+narrateur|Le filet à bagages tremble, tout bas.
+narrateur|Un manteau bleu pend, près de la porte.
+narrateur|Ça sent l'orange, tout doux.
+narrateur|Une peau repose sur la tablette.
+narrateur|Le siège pique un peu les genoux.
+narrateur|Un ticket dépasse de la poche de papa.
+narrateur|Dehors, des vaches passent, toutes lentes.
+narrateur|Maman plie un foulard bleu, sur ses genoux.
+narrateur|Nina a un sac, tout près.
+narrateur|Nina est plus grande.
+narrateur|Amir est plus petit.
+narrateur|Les tailles sont différentes.
+papa|Tu as vu les vaches, Amir ?
+enfant-m|Oui, papa.
+maman|Le foulard est pour la gare.
+narrateur|En ce moment, Amir pose un doigt sur la tablette.
+narrateur|La tablette vibre, tout doux.
+enfant-m|Viens jouer.
+copine|Oui.
+papa|On joue ensemble, d'accord ?
+enfant-m|D'accord.
+maman|Les tailles sont différentes.
+maman|Et on joue ensemble.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1354,7 +1390,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Trois coins du wagon attendent. La cuisine, le jardin, ou la chambre ? On invite. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1554,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Trois coins du wagon attendent.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On invite.
+maman|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dans le train, Kenzo va vers la cuisine du wagon. Un copain plus grand tient une brioche. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Papa sourit. On peut jouer ensemble.</t>
+          <t>Amir ouvre la tablette, tout doux. C'est la cuisine du wagon, tout petite. Une brioche sent encore le beurre. Nina est plus grande. Elle tient le sac. Amir est plus petit. Il tient une miette. Les tailles sont différentes. Viens jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. On joue ensemble. Bravo, Amir. Tu as invité. Nina casse la brioche, tout doux. Amir prend un morceau, tout petit. Merci, Nina. Merci, Amir. Une miette brille sur la tablette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,7 +1725,26 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dans le train, Kenzo va vers la cuisine du wagon. Un copain plus grand tient une brioche. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Papa sourit. On peut jouer ensemble.</t>
+          <t>narrateur|Amir ouvre la tablette, tout doux.
+narrateur|C'est la cuisine du wagon, tout petite.
+narrateur|Une brioche sent encore le beurre.
+narrateur|Nina est plus grande.
+narrateur|Elle tient le sac.
+narrateur|Amir est plus petit.
+narrateur|Il tient une miette.
+narrateur|Les tailles sont différentes.
+enfant-m|Viens jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo, Amir.
+papa|Tu as invité.
+narrateur|Nina casse la brioche, tout doux.
+narrateur|Amir prend un morceau, tout petit.
+enfant-m|Merci, Nina.
+copine|Merci, Amir.
+narrateur|Une miette brille sur la tablette.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On joue ensemble ?</t>
+          <t>Amir invite Nina. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1928,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On joue ensemble ?</t>
+          <t>narrateur|Amir invite Nina.
+papa|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Kenzo respire. Papa est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue ensemble. Les tailles sont différentes. Amir souffle une miette. On joue. Bravo. C'est du bon travail. La brioche sent encore le beurre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2101,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Kenzo respire. Papa est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+narrateur|Amir souffle une miette.
+enfant-m|On joue.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|La brioche sent encore le beurre.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2136,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, dans le sac. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2300,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, dans le sac.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2331,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose le ballon rouge sur la tablette. Un copain plus grand le fait rouler, tout doux. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le ballon rouge sur la tablette. Il est un peu trop grand, pour lui. Nina le tient, tout doux. Les tailles sont différentes. On le fait rouler ? Oui. On joue ensemble. Bravo. Le ballon roule, tout lentement. Le ballon frôle la brioche, tout doux. On est encore dans la cuisine du wagon. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2471,26 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo pose le ballon rouge sur la tablette. Un copain plus grand le fait rouler, tout doux. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Amir pose le ballon rouge sur la tablette.
+narrateur|Il est un peu trop grand, pour lui.
+narrateur|Nina le tient, tout doux.
+narrateur|Les tailles sont différentes.
+enfant-m|On le fait rouler ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Bravo.
+narrateur|Le ballon roule, tout lentement.
+narrateur|Le ballon frôle la brioche, tout doux.
+narrateur|On est encore dans la cuisine du wagon.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2515,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2683,11 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2715,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la cuisine. Puis le ballon rouge. Puis Tom. On rit un peu. Kenzo chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom a le ballon trop grand. Amir a encore le ballon rouge. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2855,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la cuisine. Puis le ballon rouge. Puis Tom. On rit un peu. Kenzo chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom a le ballon trop grand.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le ballon rouge. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3044,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3080,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de Léa. le ballon rouge est rangé. Une tasse cliquette. Kenzo essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa tient le ballon, tout lourd. Amir a encore le ballon rouge. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3220,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Une tasse cliquette. Kenzo essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa tient le ballon, tout lourd.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3269,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le ballon rouge. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3409,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3445,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un ruban reste dans la poche. Kenzo montre Sami à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami garde le ballon entre les pattes. Amir a encore le ballon rouge. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3585,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un ruban reste dans la poche. Kenzo montre Sami à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami garde le ballon entre les pattes.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3634,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le ballon rouge. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3774,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3810,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose le seau bleu entre les sièges. Un copain plus petit tient l'anse. On joue ensemble. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le seau bleu entre les sièges. Nina tient l'anse, plus haut. Amir tient le bord, plus bas. Les tailles sont différentes. On range les miettes ? Oui. Vous jouez ensemble. On joue ensemble. Le seau sonne, tout creux. Une miette tombe dans le seau bleu. On est encore dans la cuisine du wagon. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,12 +3950,26 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo pose le seau bleu entre les sièges. Un copain plus petit tient l'anse. On joue ensemble.
-papa|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Amir pose le seau bleu entre les sièges.
+narrateur|Nina tient l'anse, plus haut.
+narrateur|Amir tient le bord, plus bas.
+narrateur|Les tailles sont différentes.
+enfant-m|On range les miettes ?
+copine|Oui.
+maman|Vous jouez ensemble.
+papa|On joue ensemble.
+narrateur|Le seau sonne, tout creux.
+narrateur|Une miette tombe dans le seau bleu.
+narrateur|On est encore dans la cuisine du wagon.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3804,7 +3994,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3972,7 +4162,11 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4000,7 +4194,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de la cuisine. Kenzo s'arrête. On range un objet. Kenzo ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom regarde une miette dans le seau. Amir a encore le seau bleu. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4140,7 +4334,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Kenzo s'arrête. On range un objet. Kenzo ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom regarde une miette dans le seau.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4168,7 +4383,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le seau bleu. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4308,7 +4523,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4336,7 +4559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range le seau bleu. Léa reste près de la cuisine. Un ballon s'immobilise. Maman n'est pas loin. Kenzo les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa a une miette au foulard. Amir a encore le seau bleu. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4476,7 +4699,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range le seau bleu. Léa reste près de la cuisine. Un ballon s'immobilise. Maman n'est pas loin. Kenzo les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa a une miette au foulard.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4504,7 +4748,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le seau bleu. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4644,7 +4888,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4672,7 +4924,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Il y a des miettes sur la table. Kenzo plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami lape une miette, tout doux. Amir a encore le seau bleu. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4812,7 +5064,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Il y a des miettes sur la table. Kenzo plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami lape une miette, tout doux.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4840,7 +5113,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le seau bleu. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4980,7 +5253,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5008,7 +5289,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose le doudou sur les genoux. Un copain d'une autre taille le caresse. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le doudou sur les genoux. Nina le caresse, tout doux. Une oreille est froissée, un peu. Les tailles sont différentes. Il vient avec nous. Oui. On joue ensemble. On joue. Le doudou sent encore la maison. Le doudou a une miette sur l'oreille. On est encore dans la cuisine du wagon. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5148,7 +5429,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo pose le doudou sur les genoux. Un copain d'une autre taille le caresse. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Amir pose le doudou sur les genoux.
+narrateur|Nina le caresse, tout doux.
+narrateur|Une oreille est froissée, un peu.
+narrateur|Les tailles sont différentes.
+enfant-m|Il vient avec nous.
+copine|Oui.
+papa|On joue ensemble.
+maman|On joue.
+narrateur|Le doudou sent encore la maison.
+narrateur|Le doudou a une miette sur l'oreille.
+narrateur|On est encore dans la cuisine du wagon.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5176,7 +5469,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5344,7 +5637,11 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5372,7 +5669,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. le doudou est rangé. la cuisine est fini. On se tient la main. Kenzo pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom se colle au doudou, près de la brioche. Amir a encore le doudou. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5512,7 +5809,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la cuisine est fini. On se tient la main. Kenzo pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom se colle au doudou, près de la brioche.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5540,7 +5858,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le doudou. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5680,7 +5998,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5708,7 +6034,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Kenzo pose le doudou. la cuisine est derrière. Le vent est doux. Kenzo range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa s'assoit près du doudou. Amir a encore le doudou. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5848,7 +6174,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Kenzo pose le doudou. la cuisine est derrière. Le vent est doux. Kenzo range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa s'assoit près du doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5876,7 +6223,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le doudou. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6016,7 +6363,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6044,7 +6399,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre Sami. Papa a vu la cuisine. Et le doudou. Un chat miaule une fois. Kenzo raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami pose la crinière sur le doudou. Amir a encore le doudou. On est encore dans la cuisine du wagon. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6184,7 +6539,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre Sami. Papa a vu la cuisine. Et le doudou. Un chat miaule une fois. Kenzo raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami pose la crinière sur le doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la cuisine du wagon.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6212,7 +6588,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la cuisine du wagon. Il a tenu le doudou. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6352,7 +6728,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la cuisine du wagon.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6380,7 +6764,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Dans le train, Kenzo imagine le jardin derrière la vitre. Un copain plus petit montre un arbre. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. Je suis là. On peut jouer ensemble.</t>
+          <t>Amir colle le nez à la vitre. Derrière, un jardin défile, tout vert. Un arbre passe. Puis un autre. Nina montre un champ, plus haut. Amir montre une vache, plus bas. Les tailles sont différentes. On joue au jardin ? Oui. On joue ensemble. Bravo. Vous avez des tailles différentes. Et vous jouez ensemble. La vitre est tiède, un peu embuée. Nina souffle un rond, tout petit. J'en fais un aussi. Le corps n'est pas une blague. On joue.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6520,8 +6904,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Dans le train, Kenzo imagine le jardin derrière la vitre. Un copain plus petit montre un arbre. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes.
-papa|Je suis là. On peut jouer ensemble.</t>
+          <t>narrateur|Amir colle le nez à la vitre.
+narrateur|Derrière, un jardin défile, tout vert.
+narrateur|Un arbre passe.
+narrateur|Puis un autre.
+narrateur|Nina montre un champ, plus haut.
+narrateur|Amir montre une vache, plus bas.
+narrateur|Les tailles sont différentes.
+enfant-m|On joue au jardin ?
+copine|Oui.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Vous avez des tailles différentes.
+papa|Et vous jouez ensemble.
+narrateur|La vitre est tiède, un peu embuée.
+narrateur|Nina souffle un rond, tout petit.
+enfant-m|J'en fais un aussi.
+maman|Le corps n'est pas une blague.
+maman|On joue.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6709,7 +7109,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
+          <t>narrateur|Les tailles sont différentes.
+maman|On fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6737,7 +7138,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Kenzo retient le geste. Papa sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue ensemble. Les tailles sont différentes. Amir touche le rond sur la vitre. Ensemble. Bravo. Tu as fait du bon travail. Une vache passe encore, tout loin.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6881,7 +7282,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Kenzo retient le geste. Papa sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+narrateur|Amir touche le rond sur la vitre.
+enfant-m|Ensemble.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Une vache passe encore, tout loin.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6909,7 +7317,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, dans le sac. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7073,7 +7481,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, dans le sac.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7101,7 +7512,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kenzo fait rouler le ballon rouge près de la vitre. Un copain plus grand le rattrape. Les tailles sont différentes. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le ballon rouge sur la tablette. Il est un peu trop grand, pour lui. Nina le tient, tout doux. Les tailles sont différentes. On le fait rouler ? Oui. On joue ensemble. Bravo. Le ballon roule, tout lentement. Le ballon attrape un reflet de champ. On est encore dans le jardin derrière la vitre. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7241,12 +7652,26 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo fait rouler le ballon rouge près de la vitre. Un copain plus grand le rattrape. Les tailles sont différentes.
-papa|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Amir pose le ballon rouge sur la tablette.
+narrateur|Il est un peu trop grand, pour lui.
+narrateur|Nina le tient, tout doux.
+narrateur|Les tailles sont différentes.
+enfant-m|On le fait rouler ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Bravo.
+narrateur|Le ballon roule, tout lentement.
+narrateur|Le ballon attrape un reflet de champ.
+narrateur|On est encore dans le jardin derrière la vitre.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7696,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7864,11 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7896,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le jardin. Puis le ballon rouge. Puis Tom. On dit merci. Kenzo souffle, puis sourit à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom suit le champ, près du ballon. Amir a encore le ballon rouge. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,7 +8036,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le jardin. Puis le ballon rouge. Puis Tom. On dit merci. Kenzo souffle, puis sourit à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom suit le champ, près du ballon.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7635,7 +8085,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le ballon rouge. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8225,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8261,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de Léa. le ballon rouge est rangé. Le sol est un peu froid. Kenzo serre la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa a le ballon contre la vitre. Amir a encore le ballon rouge. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,7 +8401,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Le sol est un peu froid. Kenzo serre la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa a le ballon contre la vitre.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7971,7 +8450,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le ballon rouge. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8590,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8626,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de le jardin. Et de le ballon rouge. Et de Sami. Une cloche tinte, tout loin. Kenzo range le jardin dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami roule un peu, comme le ballon. Amir a encore le ballon rouge. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,7 +8766,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de le jardin. Et de le ballon rouge. Et de Sami. Une cloche tinte, tout loin. Kenzo range le jardin dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami roule un peu, comme le ballon.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8307,7 +8815,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le ballon rouge. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +8955,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +8991,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose le seau bleu. Un copain plus petit rit un peu. Les tailles sont différentes. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le seau bleu entre les sièges. Nina tient l'anse, plus haut. Amir tient le bord, plus bas. Les tailles sont différentes. On range les miettes ? Oui. Vous jouez ensemble. On joue ensemble. Le seau sonne, tout creux. Le seau bleu se colle à la vitre tiède. On est encore dans le jardin derrière la vitre. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +9131,26 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo pose le seau bleu. Un copain plus petit rit un peu. Les tailles sont différentes. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Amir pose le seau bleu entre les sièges.
+narrateur|Nina tient l'anse, plus haut.
+narrateur|Amir tient le bord, plus bas.
+narrateur|Les tailles sont différentes.
+enfant-m|On range les miettes ?
+copine|Oui.
+maman|Vous jouez ensemble.
+papa|On joue ensemble.
+narrateur|Le seau sonne, tout creux.
+narrateur|Le seau bleu se colle à la vitre tiède.
+narrateur|On est encore dans le jardin derrière la vitre.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +9175,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9343,11 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9375,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de le jardin. Kenzo s'arrête. Un galet est encore chaud. Kenzo s'assoit près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom a l'oreille froide, près du seau. Amir a encore le seau bleu. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,7 +9515,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Kenzo s'arrête. Un galet est encore chaud. Kenzo s'assoit près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom a l'oreille froide, près du seau.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9007,7 +9564,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le seau bleu. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9704,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9740,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range le seau bleu. Léa reste près de le jardin. Une feuille tombe. Kenzo range encore un peu, près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa voit une vache dans le seau. Amir a encore le seau bleu. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,7 +9880,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range le seau bleu. Léa reste près de le jardin. Une feuille tombe. Kenzo range encore un peu, près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa voit une vache dans le seau.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9343,7 +9929,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le seau bleu. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +10069,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10105,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Ça sent le pain chaud. Kenzo ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami écoute le seau, tout creux. Amir a encore le seau bleu. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,7 +10245,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Ça sent le pain chaud. Kenzo ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami écoute le seau, tout creux.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9679,7 +10294,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le seau bleu. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10434,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10470,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Kenzo assoit le doudou. Un copain d'une autre taille chuchote. Les tailles sont différentes. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le doudou sur les genoux. Nina le caresse, tout doux. Une oreille est froissée, un peu. Les tailles sont différentes. Il vient avec nous. Oui. On joue ensemble. On joue. Le doudou sent encore la maison. Le doudou regarde les vaches, tout calme. On est encore dans le jardin derrière la vitre. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,7 +10610,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo assoit le doudou. Un copain d'une autre taille chuchote. Les tailles sont différentes. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Amir pose le doudou sur les genoux.
+narrateur|Nina le caresse, tout doux.
+narrateur|Une oreille est froissée, un peu.
+narrateur|Les tailles sont différentes.
+enfant-m|Il vient avec nous.
+copine|Oui.
+papa|On joue ensemble.
+maman|On joue.
+narrateur|Le doudou sent encore la maison.
+narrateur|Le doudou regarde les vaches, tout calme.
+narrateur|On est encore dans le jardin derrière la vitre.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10015,7 +10650,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10818,11 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +10850,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. le doudou est rangé. le jardin est fini. On écoute jusqu'au bout. Kenzo dit merci à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom et le doudou regardent le jardin. Amir a encore le doudou. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,7 +10990,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. le jardin est fini. On écoute jusqu'au bout. Kenzo dit merci à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom et le doudou regardent le jardin.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10379,7 +11039,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le doudou. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11179,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11215,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Kenzo pose le doudou. le jardin est derrière. Le savon sent bon. Kenzo boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa a le foulard comme le doudou. Amir a encore le doudou. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,7 +11355,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Kenzo pose le doudou. le jardin est derrière. Le savon sent bon. Kenzo boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa a le foulard comme le doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10715,7 +11404,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le doudou. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11544,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11580,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre Sami. Papa a vu le jardin. Et le doudou. Un linge sèche à l'air. Kenzo caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami chauffe contre le doudou. Amir a encore le doudou. On est encore dans le jardin derrière la vitre. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,7 +11720,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre Sami. Papa a vu le jardin. Et le doudou. Un linge sèche à l'air. Kenzo caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami chauffe contre le doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans le jardin derrière la vitre.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11051,7 +11769,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans le jardin derrière la vitre. Il a tenu le doudou. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +11909,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans le jardin derrière la vitre.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +11945,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Dans le train, Kenzo ouvre un livre de chambre. Un copain d'une autre taille s'assoit. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+          <t>Amir plie le manteau bleu, sur le siège. C'est une chambre, tout minuscule. Nina pose le sac comme un oreiller. Nina est plus grande. Le sac est grand. Amir est plus petit. Il a le doudou. Les tailles sont différentes. On joue à la chambre ? Oui. On invite. On joue ensemble. Bravo, Amir. Le manteau sent encore la pluie. Nina baisse un peu le col. C'est doux.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,7 +12085,22 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Dans le train, Kenzo ouvre un livre de chambre. Un copain d'une autre taille s'assoit. Kenzo l'invite. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+          <t>narrateur|Amir plie le manteau bleu, sur le siège.
+narrateur|C'est une chambre, tout minuscule.
+narrateur|Nina pose le sac comme un oreiller.
+narrateur|Nina est plus grande.
+narrateur|Le sac est grand.
+narrateur|Amir est plus petit.
+narrateur|Il a le doudou.
+narrateur|Les tailles sont différentes.
+enfant-m|On joue à la chambre ?
+copine|Oui.
+papa|On invite.
+maman|On joue ensemble.
+papa|Bravo, Amir.
+narrateur|Le manteau sent encore la pluie.
+narrateur|Nina baisse un peu le col.
+enfant-m|C'est doux.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11387,7 +12128,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On invite, et on joue ensemble ?</t>
+          <t>Amir a invité Nina. On invite, et on joue ensemble ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11543,7 +12284,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On invite, et on joue ensemble ?</t>
+          <t>narrateur|Amir a invité Nina.
+papa|On invite, et on joue ensemble ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11571,7 +12313,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Kenzo hoche la tête. On continue, avec papa. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On invite. On joue ensemble. Les tailles sont différentes. Amir caresse le manteau, tout doux. On joue. Bravo, Amir. C'est du bon travail. Le sac fait un petit creux.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11715,7 +12457,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Kenzo hoche la tête. On continue, avec papa. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On invite.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+narrateur|Amir caresse le manteau, tout doux.
+enfant-m|On joue.
+maman|Bravo, Amir.
+maman|C'est du bon travail.
+narrateur|Le sac fait un petit creux.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11743,7 +12493,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, dans le sac. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11907,7 +12657,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, dans le sac.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11935,7 +12688,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kenzo fait un train : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le ballon rouge sur la tablette. Il est un peu trop grand, pour lui. Nina le tient, tout doux. Les tailles sont différentes. On le fait rouler ? Oui. On joue ensemble. Bravo. Le ballon roule, tout lentement. Le ballon s'adosse au manteau bleu. On est encore dans la petite chambre du siège. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12075,10 +12828,26 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo fait un train : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. On joue ensemble. Papa reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Amir pose le ballon rouge sur la tablette.
+narrateur|Il est un peu trop grand, pour lui.
+narrateur|Nina le tient, tout doux.
+narrateur|Les tailles sont différentes.
+enfant-m|On le fait rouler ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Bravo.
+narrateur|Le ballon roule, tout lentement.
+narrateur|Le ballon s'adosse au manteau bleu.
+narrateur|On est encore dans la petite chambre du siège.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12103,7 +12872,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12271,7 +13040,11 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12299,7 +13072,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la chambre. Puis le ballon rouge. Puis Tom. Une chaussette est encore sablée. Kenzo tend Tom à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom s'adosse au manteau, près du ballon. Amir a encore le ballon rouge. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12439,7 +13212,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la chambre. Puis le ballon rouge. Puis Tom. Une chaussette est encore sablée. Kenzo tend Tom à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom s'adosse au manteau, près du ballon.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12467,7 +13261,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le ballon rouge. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12607,7 +13401,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12635,7 +13437,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kenzo s'arrête près de Léa. le ballon rouge est rangé. Un vélo passe au loin. J'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa a le ballon sur le sac. Amir a encore le ballon rouge. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12775,9 +13577,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo s'arrête près de Léa. le ballon rouge est rangé. Un vélo passe au loin.
-enfant-m|J'ai appris.
-narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa a le ballon sur le sac.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12805,7 +13626,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le ballon rouge. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12945,7 +13766,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12973,7 +13802,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Kenzo se souvient de la chambre. Et de le ballon rouge. Et de Sami. On entend un oiseau. Kenzo écoute papa encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami garde le ballon, tout calme. Amir a encore le ballon rouge. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13113,7 +13942,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo se souvient de la chambre. Et de le ballon rouge. Et de Sami. On entend un oiseau. Kenzo écoute papa encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami garde le ballon, tout calme.
+narrateur|Amir a encore le ballon rouge.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13141,7 +13991,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le ballon rouge. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13281,7 +14131,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le ballon rouge.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13309,7 +14167,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Kenzo cache le seau bleu sous le siège. Un copain plus petit le retrouve. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le seau bleu entre les sièges. Nina tient l'anse, plus haut. Amir tient le bord, plus bas. Les tailles sont différentes. On range les miettes ? Oui. Vous jouez ensemble. On joue ensemble. Le seau sonne, tout creux. Le seau bleu sert de table, tout petit. On est encore dans la petite chambre du siège. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13449,10 +14307,26 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo cache le seau bleu sous le siège. Un copain plus petit le retrouve. On joue ensemble. Papa montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Amir pose le seau bleu entre les sièges.
+narrateur|Nina tient l'anse, plus haut.
+narrateur|Amir tient le bord, plus bas.
+narrateur|Les tailles sont différentes.
+enfant-m|On range les miettes ?
+copine|Oui.
+maman|Vous jouez ensemble.
+papa|On joue ensemble.
+narrateur|Le seau sonne, tout creux.
+narrateur|Le seau bleu sert de table, tout petit.
+narrateur|On est encore dans la petite chambre du siège.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13477,7 +14351,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13645,7 +14519,11 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13673,7 +14551,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de la chambre. Kenzo s'arrête. Les chaussures font toc toc. Kenzo répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom a un ticket dans le seau. Amir a encore le seau bleu. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13813,7 +14691,28 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Kenzo s'arrête. Les chaussures font toc toc. Kenzo répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom a un ticket dans le seau.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13841,7 +14740,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le seau bleu. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13981,7 +14880,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14009,7 +14916,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Kenzo range le seau bleu. Léa reste près de la chambre. Une pomme brille un peu. Kenzo marche près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa tient le seau, trop lourd. Amir a encore le seau bleu. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14149,7 +15056,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo range le seau bleu. Léa reste près de la chambre. Une pomme brille un peu. Kenzo marche près de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa tient le seau, trop lourd.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14177,7 +15105,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le seau bleu. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14317,7 +15245,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14345,7 +15281,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. La couverture est douce. Kenzo enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami a la crinière dans le seau. Amir a encore le seau bleu. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14485,7 +15421,28 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. La couverture est douce. Kenzo enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami a la crinière dans le seau.
+narrateur|Amir a encore le seau bleu.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14513,7 +15470,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le seau bleu. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14653,7 +15610,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le seau bleu.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14681,7 +15646,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Kenzo calce le doudou. Un copain d'une autre taille sourit. Les tailles sont différentes. On joue ensemble. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Amir pose le doudou sur les genoux. Nina le caresse, tout doux. Une oreille est froissée, un peu. Les tailles sont différentes. Il vient avec nous. Oui. On joue ensemble. On joue. Le doudou sent encore la maison. Le doudou s'endort sur le sac. On est encore dans la petite chambre du siège. Les tailles sont différentes. On joue ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14821,9 +15786,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo calce le doudou. Un copain d'une autre taille sourit. Les tailles sont différentes. On joue ensemble.
-papa|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Amir pose le doudou sur les genoux.
+narrateur|Nina le caresse, tout doux.
+narrateur|Une oreille est froissée, un peu.
+narrateur|Les tailles sont différentes.
+enfant-m|Il vient avec nous.
+copine|Oui.
+papa|On joue ensemble.
+maman|On joue.
+narrateur|Le doudou sent encore la maison.
+narrateur|Le doudou s'endort sur le sac.
+narrateur|On est encore dans la petite chambre du siège.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14851,7 +15826,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, sur le siège. Tom, Léa, ou Sami ? Les tailles sont différentes. On joue ensemble. Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15019,7 +15994,11 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, sur le siège.
+maman|Tom, Léa, ou Sami ?
+papa|Les tailles sont différentes.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15047,7 +16026,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. le doudou est rangé. la chambre est fini. Un crochet tient bien le manteau. Kenzo sourit. Papa sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend l'ours Tom. Un ticket est glissé dans la poche. L'oreille est rêche, puis douce. Tom vient jouer. Oui. Vous jouez ensemble. Les tailles sont différentes. Bravo, Amir. L'ours Tom s'assoit contre le genou. L'ours Tom et le doudou partagent le manteau. Amir a encore le doudou. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15187,7 +16166,28 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. le doudou est rangé. la chambre est fini. Un crochet tient bien le manteau. Kenzo sourit. Papa sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend l'ours Tom.
+narrateur|Un ticket est glissé dans la poche.
+narrateur|L'oreille est rêche, puis douce.
+enfant-m|Tom vient jouer.
+copine|Oui.
+papa|Vous jouez ensemble.
+maman|Les tailles sont différentes.
+papa|Bravo, Amir.
+narrateur|L'ours Tom s'assoit contre le genou.
+narrateur|L'ours Tom et le doudou partagent le manteau.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range l'ours Tom, tout doux.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15215,7 +16215,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le doudou. Il a parlé près de l'ours Tom. L'ours Tom garde le ticket, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15355,7 +16355,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de l'ours Tom.
+narrateur|L'ours Tom garde le ticket, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15383,7 +16391,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Kenzo pose le doudou. la chambre est derrière. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend la poupée Léa. Elle a un foulard, tout minuscule. Un bouton brille, comme la vitre. Léa vient avec nous. Oui. On joue ensemble. Les tailles sont différentes. Bravo. La poupée Léa penche la tête. La poupée Léa s'endort presque, près du doudou. Amir a encore le doudou. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15523,7 +16531,28 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Kenzo pose le doudou. la chambre est derrière. L'eau coule, tout petit bruit. Kenzo pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend la poupée Léa.
+narrateur|Elle a un foulard, tout minuscule.
+narrateur|Un bouton brille, comme la vitre.
+enfant-m|Léa vient avec nous.
+copine|Oui.
+maman|On joue ensemble.
+papa|Les tailles sont différentes.
+maman|Bravo.
+narrateur|La poupée Léa penche la tête.
+narrateur|La poupée Léa s'endort presque, près du doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range la poupée Léa, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15551,7 +16580,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le doudou. Il a parlé près de la poupée Léa. La poupée Léa garde son foulard droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15691,7 +16720,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son foulard droit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15719,7 +16756,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kenzo montre Sami. Papa a vu la chambre. Et le doudou. La lumière est claire. Kenzo prend la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>Amir prend le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde les champs. Sami joue aussi. Oui. On joue ensemble. Le corps n'est pas une blague. On joue. Le lion Sami chauffe contre la vitre. Le lion Sami écoute le wagon, près du doudou. Amir a encore le doudou. On est encore dans la petite chambre du siège. On joue encore ? Oui. On joue ensemble. Les tailles sont différentes. Le corps n'est pas une blague. Bravo, Amir. Tu as fait du bon travail. Merci, papa. Merci, maman. Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15859,7 +16896,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo montre Sami. Papa a vu la chambre. Et le doudou. La lumière est claire. Kenzo prend la main de papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Kenzo dit merci à papa.</t>
+          <t>narrateur|Amir prend le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde les champs.
+enfant-m|Sami joue aussi.
+copine|Oui.
+papa|On joue ensemble.
+maman|Le corps n'est pas une blague.
+maman|On joue.
+narrateur|Le lion Sami chauffe contre la vitre.
+narrateur|Le lion Sami écoute le wagon, près du doudou.
+narrateur|Amir a encore le doudou.
+narrateur|On est encore dans la petite chambre du siège.
+enfant-m|On joue encore ?
+copine|Oui.
+papa|On joue ensemble.
+maman|Les tailles sont différentes.
+maman|Le corps n'est pas une blague.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Amir range le lion Sami, tout doux.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15887,7 +16945,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Amir. Tu as fait du bon travail. Amir a joué dans la petite chambre du siège. Il a tenu le doudou. Il a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16027,7 +17085,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+copine|Oui.
+maman|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|Amir a joué dans la petite chambre du siège.
+narrateur|Il a tenu le doudou.
+narrateur|Il a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16049,7 +17115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16143,6 +17209,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-009.xlsx
+++ b/stories/arbres/TREE-DIF-009.xlsx
@@ -1197,12 +1197,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le plancher, les joints font tic, puis tac. Le wagon sent l'orange, encore un peu. Un ticket dépasse de la poche de papa. Dehors, un champ passe, tout vert. Le filet à bagages tremble, tout bas. Tu entends les rails, Amir ? Ils chantent. Le grand train va loin, ce matin. Nina pose un sac de toile, près des genoux. Dedans, des rails de bois s'entrechoquent. Je veux un petit train, comme le grand. Tu le poses où, alors ? Près des rails, avec Nina. Les pièces sont dans le sac. En ce moment, Amir sort une locomotive en bois. Elle est petite, toute lisse. J'ai les rails. On fait une longue voie. Jaune, bleu, ou rouge ?</t>
+          <t>Sous le plancher, les joints font tic, puis tac. Tu entends les rails, Amir ? Ils chantent. Le wagon sent l'orange, encore un peu. Un ticket dépasse de la poche de papa, sous le filet. Le grand train va loin, ce matin. Dehors, un champ passe, tout vert, derrière la vitre. Nina pose un sac de toile, près des genoux. Dedans, des rails de bois s'entrechoquent. Je veux un petit train, comme le grand. Tu le poses où, alors ? Près des rails, avec Nina. Les pièces sont dans le sac. En ce moment, Amir sort une locomotive en bois. Elle est petite, toute lisse. J'ai les rails. On fait une longue voie. Jaune, bleu, ou rouge ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Sous le plancher, les joints font tic, puis tac. Le wagon sent l'orange, encore un peu. Un ticket dépasse de la poche de papa. Dehors, un champ passe, tout vert. Le filet à bagages tremble, tout bas. Tu entends les rails, Amir ? Ils chantent. Le grand train va loin, ce matin. Nina pose un sac de toile, près des genoux. Dedans, des rails de bois s'entrechoquent. Je veux un petit train, comme le grand. Tu le poses où, alors ? Près des rails, avec Nina. Les pièces sont dans le sac. En ce moment, Amir sort une locomotive en bois. Elle est petite, toute lisse. J'ai les rails. On fait une longue voie. Jaune, bleu, ou rouge ?</t>
+          <t>Sous le plancher, les joints font tic, puis tac. Tu entends les rails, Amir ? Ils chantent. Le wagon sent l'orange, encore un peu. Un ticket dépasse de la poche de papa, sous le filet. Le grand train va loin, ce matin. Dehors, un champ passe, tout vert, derrière la vitre. Nina pose un sac de toile, près des genoux. Dedans, des rails de bois s'entrechoquent. Je veux un petit train, comme le grand. Tu le poses où, alors ? Près des rails, avec Nina. Les pièces sont dans le sac. En ce moment, Amir sort une locomotive en bois. Elle est petite, toute lisse. J'ai les rails. On fait une longue voie. Jaune, bleu, ou rouge ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1338,13 +1338,12 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Sous le plancher, les joints font tic, puis tac.
-narrateur|Le wagon sent l'orange, encore un peu.
-narrateur|Un ticket dépasse de la poche de papa.
-narrateur|Dehors, un champ passe, tout vert.
-narrateur|Le filet à bagages tremble, tout bas.
 papa|Tu entends les rails, Amir ?
 enfant-m|Ils chantent.
+narrateur|Le wagon sent l'orange, encore un peu.
+narrateur|Un ticket dépasse de la poche de papa, sous le filet.
 maman|Le grand train va loin, ce matin.
+narrateur|Dehors, un champ passe, tout vert, derrière la vitre.
 narrateur|Nina pose un sac de toile, près des genoux.
 narrateur|Dedans, des rails de bois s'entrechoquent.
 enfant-m|Je veux un petit train, comme le grand.
@@ -2307,12 +2306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amir pose un pont de bois au-dessus de l'ombre. Les pieds du pont touchent le plancher jaune. Le haut est trop loin. Tes bras sont plus courts, c'est tout. Nina tend les siens, jusqu'à la planche. Je tiens le milieu, moi. Moi, les pieds. Vous le tenez, chacun un bout. Le pont tremble un peu, puis tient.</t>
+          <t>Amir pose un pont de bois au-dessus de l'ombre. Les pieds du pont touchent le plancher jaune. Le haut est trop loin. La planche est un peu haute. Nina tend les siens, jusqu'à la planche. Je tiens le milieu, moi. Moi, les pieds. Vous le tenez, chacun un bout. Le pont tremble un peu, puis tient.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Amir pose un pont de bois au-dessus de l'ombre. Les pieds du pont touchent le plancher jaune. Le haut est trop loin. Tes bras sont plus courts, c'est tout. Nina tend les siens, jusqu'à la planche. Je tiens le milieu, moi. Moi, les pieds. Vous le tenez, chacun un bout. Le pont tremble un peu, puis tient.</t>
+          <t>Amir pose un pont de bois au-dessus de l'ombre. Les pieds du pont touchent le plancher jaune. Le haut est trop loin. La planche est un peu haute. Nina tend les siens, jusqu'à la planche. Je tiens le milieu, moi. Moi, les pieds. Vous le tenez, chacun un bout. Le pont tremble un peu, puis tient.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2450,7 +2449,7 @@
           <t>narrateur|Amir pose un pont de bois au-dessus de l'ombre.
 narrateur|Les pieds du pont touchent le plancher jaune.
 enfant-m|Le haut est trop loin.
-papa|Tes bras sont plus courts, c'est tout.
+papa|La planche est un peu haute.
 narrateur|Nina tend les siens, jusqu'à la planche.
 enfant-f|Je tiens le milieu, moi.
 enfant-m|Moi, les pieds.
@@ -4791,12 +4790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sous les sièges. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sous les sièges. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sous les sièges. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sous les sièges. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4936,7 +4935,7 @@
 enfant-f|Moi, je garde le toit.
 narrateur|La locomotive roule, puis touche la pierre.
 maman|Elle s'arrête sous les sièges.
-papa|Deux hauteurs, un seul train.
+papa|Le galet l'a retenue.
 enfant-m|Elle est à la gare.</t>
         </is>
       </c>
@@ -9766,12 +9765,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête le long de la vitre. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête le long de la vitre. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête le long de la vitre. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête le long de la vitre. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -9911,7 +9910,7 @@
 enfant-f|Moi, je garde le toit.
 narrateur|La locomotive roule, puis touche la pierre.
 maman|Elle s'arrête le long de la vitre.
-papa|Deux hauteurs, un seul train.
+papa|Le galet l'a retenue.
 enfant-m|Elle est à la gare.</t>
         </is>
       </c>
@@ -14737,12 +14736,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sur la valise. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sur la valise. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sur la valise. Deux hauteurs, un seul train. Elle est à la gare.</t>
+          <t>Le galet, pour arrêter. Amir le pose au quai, tout près du sol. Moi, je garde le toit. La locomotive roule, puis touche la pierre. Elle s'arrête sur la valise. Le galet l'a retenue. Elle est à la gare.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -14882,7 +14881,7 @@
 enfant-f|Moi, je garde le toit.
 narrateur|La locomotive roule, puis touche la pierre.
 maman|Elle s'arrête sur la valise.
-papa|Deux hauteurs, un seul train.
+papa|Le galet l'a retenue.
 enfant-m|Elle est à la gare.</t>
         </is>
       </c>
@@ -16487,7 +16486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16593,6 +16592,13 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/TREE-DIF-009.xlsx
+++ b/stories/arbres/TREE-DIF-009.xlsx
@@ -4631,17 +4631,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>La plume, sur le toit. Nina glisse la plume au faîte, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près.</t>
+          <t>La plume, sur le toit. Nina glisse la plume au toit, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, sur le toit. Nina glisse la plume au faîte, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, sur le toit. Nina glisse la plume au toit, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, sur le toit. Nina glisse la plume au faîte, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près. [pause]</t>
+          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, sur le toit. Nina glisse la plume au toit, haute. Amir pousse depuis le plancher, lent. Je la vois. La plume tremble, puis s'arrête. Le train s'aligne sous le blanc. Deux hauteurs tiennent la gare. Vous l'avez posé, chacun son bout. L'éclat de ticket se loge sous la plume. Le pied de la chaise est tout près. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       <c r="AW20" t="inlineStr">
         <is>
           <t>enfant-m|La plume, sur le toit.
-narrateur|Nina glisse la plume au faîte, haute.
+narrateur|Nina glisse la plume au toit, haute.
 narrateur|Amir pousse depuis le plancher, lent.
 enfant-f|Je la vois.
 narrateur|La plume tremble, puis s'arrête.
@@ -4816,17 +4816,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'éclat de ticket se loge sous la plume du faîte.</t>
+          <t>Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'éclat de ticket se loge sous la plume du toit.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du faîte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du toit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du faîte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le toit a failli rester trop haut. Le petit train s'aligne sous la chaise, sous la plume. Je l'ai posée. Moi, j'ai poussé. Chacun son bout, chacun sa hauteur. Le quai jaune touche presque le pied. Les grands rails chantent, tout bas. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du toit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
 papa|Chacun son bout, chacun sa hauteur.
 maman|Le quai jaune touche presque le pied.
 narrateur|Les grands rails chantent, tout bas.
-narrateur|L'éclat de ticket se loge sous la plume du faîte.</t>
+narrateur|L'éclat de ticket se loge sous la plume du toit.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -9541,17 +9541,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le grelot, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez hissé, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette.</t>
+          <t>Le grelot, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez monté, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;grelot&lt;/emphasis&gt;, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez hissé, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;grelot&lt;/emphasis&gt;, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez monté, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;grelot&lt;/emphasis&gt;, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez hissé, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette. [pause]</t>
+          <t>Le &lt;emphasis&gt;grelot&lt;/emphasis&gt;, en haut. Nina pose le grelot sur le toit de gare. Amir pousse depuis le plancher, lent. Quand ça tinte, tu es prête. Le grelot tinte, trop haut pour lui. Nina reçoit le train, à sa hauteur. La gare des nuages n'est plus trop haute. Vous l'avez monté, chacun son étage. L'éclat de ticket tinte avec le grelot. La chaise est juste sous la tablette. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9692,7 +9692,7 @@
 narrateur|Le grelot tinte, trop haut pour lui.
 narrateur|Nina reçoit le train, à sa hauteur.
 narrateur|La gare des nuages n'est plus trop haute.
-maman|Vous l'avez hissé, chacun son étage.
+maman|Vous l'avez monté, chacun son étage.
 narrateur|L'éclat de ticket tinte avec le grelot.
 papa|La chaise est juste sous la tablette.</t>
         </is>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>La gare a failli rester trop haute. Le petit train est sous la chaise, hissé au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'éclat de ticket tinte, caché sous le grelot du toit.</t>
+          <t>La gare a failli rester trop haute. Le petit train est sous la chaise, monté au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'éclat de ticket tinte, caché sous le grelot du toit.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La gare a failli rester trop haute. Le petit train est sous la chaise, hissé au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; tinte, caché sous le grelot du toit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La gare a failli rester trop haute. Le petit train est sous la chaise, monté au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; tinte, caché sous le grelot du toit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La gare a failli rester trop haute. Le petit train est sous la chaise, hissé au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; tinte, caché sous le grelot du toit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La gare a failli rester trop haute. Le petit train est sous la chaise, monté au tintement. Tu étais en haut. J'ai entendu. Le grelot a parlé d'un étage à l'autre. La tablette froide est devenue un quai. Les grands rails chantent, sous les nuages. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; tinte, caché sous le grelot du toit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
       <c r="AW47" t="inlineStr">
         <is>
           <t>narrateur|La gare a failli rester trop haute.
-narrateur|Le petit train est sous la chaise, hissé au tintement.
+narrateur|Le petit train est sous la chaise, monté au tintement.
 enfant-m|Tu étais en haut.
 enfant-f|J'ai entendu.
 papa|Le grelot a parlé d'un étage à l'autre.
@@ -9913,17 +9913,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>La plume, pour le ciel. Nina plante la plume au faîte, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette.</t>
+          <t>La plume, pour le ciel. Nina plante la plume au toit, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, pour le ciel. Nina plante la plume au faîte, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, pour le ciel. Nina plante la plume au toit, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, pour le ciel. Nina plante la plume au faîte, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette. [pause]</t>
+          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, pour le ciel. Nina plante la plume au toit, contre le verre. Amir vise le blanc, d'en bas. C'est ici. Le train grimpe, lent, vers la plume. Deux hauteurs se rejoignent au quai. Le ciel pâle reste collé au toit. Vous l'avez visé, de loin. L'éclat de ticket se loge sous la plume. Le pied de la chaise touche la tablette. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10058,7 +10058,7 @@
       <c r="AW48" t="inlineStr">
         <is>
           <t>enfant-m|La plume, pour le ciel.
-narrateur|Nina plante la plume au faîte, contre le verre.
+narrateur|Nina plante la plume au toit, contre le verre.
 narrateur|Amir vise le blanc, d'en bas.
 enfant-f|C'est ici.
 narrateur|Le train grimpe, lent, vers la plume.
@@ -10098,17 +10098,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'éclat de ticket se loge sous la plume du faîte bleu.</t>
+          <t>Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'éclat de ticket se loge sous la plume du toit bleu.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du faîte bleu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du toit bleu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du faîte bleu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ciel a failli cacher le quai. Le petit train s'aligne sous la chaise, sous la plume. C'était ici. Je visais le blanc. Deux hauteurs ont visé le même toit. Le verre garde un fil de plume. Les grands rails chantent, contre le ciel. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; se loge sous la plume du toit bleu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10253,7 +10253,7 @@
 papa|Deux hauteurs ont visé le même toit.
 maman|Le verre garde un fil de plume.
 narrateur|Les grands rails chantent, contre le ciel.
-narrateur|L'éclat de ticket se loge sous la plume du faîte bleu.</t>
+narrateur|L'éclat de ticket se loge sous la plume du toit bleu.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le galet, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez hissé, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains.</t>
+          <t>Le galet, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez monté, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;galet&lt;/emphasis&gt;, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez hissé, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;galet&lt;/emphasis&gt;, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez monté, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;galet&lt;/emphasis&gt;, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez hissé, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains. [pause]</t>
+          <t>Le &lt;emphasis&gt;galet&lt;/emphasis&gt;, pour pas reculer. Amir cale le galet derrière les roues. Nina tire le train, d'en haut, douce. Je pousse, toi tu tires. Le galet empêche de redescendre. Le train gagne le quai, lent. La tablette froide devient une gare. Vous l'avez monté, sans le lâcher. L'éclat de ticket reste derrière le galet. La chaise est là, sous vos mains. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10436,7 +10436,7 @@
 narrateur|Le galet empêche de redescendre.
 narrateur|Le train gagne le quai, lent.
 narrateur|La tablette froide devient une gare.
-maman|Vous l'avez hissé, sans le lâcher.
+maman|Vous l'avez monté, sans le lâcher.
 narrateur|L'éclat de ticket reste derrière le galet.
 papa|La chaise est là, sous vos mains.</t>
         </is>
@@ -13687,17 +13687,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>La plume, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train gravit la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente.</t>
+          <t>La plume, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train monte la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train gravit la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;plume&lt;/emphasis&gt;, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train monte la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train gravit la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente. [pause]</t>
+          <t>La &lt;emphasis&gt;plume&lt;/emphasis&gt;, sur la poignée. Nina plante la plume, tout en haut. Amir vise le blanc, depuis le tapis. Monte. Le train monte la pente, sous la plume. La fermeture reste close, sans danser. Deux hauteurs tiennent le pont de tissu. Vous l'avez visé, de la poignée au tapis. L'éclat de ticket se colle à la plume. La chaise attend, après la descente. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13835,7 +13835,7 @@
 narrateur|Nina plante la plume, tout en haut.
 narrateur|Amir vise le blanc, depuis le tapis.
 enfant-f|Monte.
-narrateur|Le train gravit la pente, sous la plume.
+narrateur|Le train monte la pente, sous la plume.
 narrateur|La fermeture reste close, sans danser.
 narrateur|Deux hauteurs tiennent le pont de tissu.
 maman|Vous l'avez visé, de la poignée au tapis.
@@ -13872,17 +13872,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au faîte. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'éclat de ticket voyage, collé à la plume de poignée.</t>
+          <t>La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au toit. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'éclat de ticket voyage, collé à la plume de poignée.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au faîte. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; voyage, collé à la plume de poignée.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au toit. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'&lt;emphasis level="moderate"&gt;éclat de ticket&lt;/emphasis&gt; voyage, collé à la plume de poignée.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au faîte. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; voyage, collé à la plume de poignée.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poignée a failli rester trop loin. Le petit train arrive sous la chaise, plume au toit. Monte, j'ai dit. J'ai visé. Le blanc a relié le tapis à la poignée. Le tissu rêche garde un fil de plume. Les grands rails chantent, sous la valise. L'&lt;emphasis&gt;éclat de ticket&lt;/emphasis&gt; voyage, collé à la plume de poignée.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -14021,7 +14021,7 @@
       <c r="AW69" t="inlineStr">
         <is>
           <t>narrateur|La poignée a failli rester trop loin.
-narrateur|Le petit train arrive sous la chaise, plume au faîte.
+narrateur|Le petit train arrive sous la chaise, plume au toit.
 enfant-f|Monte, j'ai dit.
 enfant-m|J'ai visé.
 papa|Le blanc a relié le tapis à la poignée.
@@ -17439,7 +17439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17559,6 +17559,13 @@
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
